--- a/data/project_tasks.xlsx
+++ b/data/project_tasks.xlsx
@@ -1,17 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21001"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\WW FILES\Indie Project\gantt-plotter\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E275D26C-4E60-45D0-95EE-DAF22B6E1724}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="0" yWindow="36" windowWidth="15960" windowHeight="18084" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId4"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="PROJECT" sheetId="3" r:id="rId2"/>
+    <sheet name="CES" sheetId="2" r:id="rId3"/>
+    <sheet name="SD" sheetId="4" r:id="rId4"/>
+    <sheet name="FT" sheetId="5" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="179021"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="140">
   <si>
     <t>task_id</t>
   </si>
@@ -248,31 +261,209 @@
   </si>
   <si>
     <t>Create loyalty program</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Structure Geometry</t>
+  </si>
+  <si>
+    <t>Boundary Condition</t>
+  </si>
+  <si>
+    <t>Tendon</t>
+  </si>
+  <si>
+    <t>Bridge Loading</t>
+  </si>
+  <si>
+    <t>Construction Sequence &amp; Method</t>
+  </si>
+  <si>
+    <t>SSI Parameter</t>
+  </si>
+  <si>
+    <t>duration_days</t>
+  </si>
+  <si>
+    <t>Review section input</t>
+  </si>
+  <si>
+    <t>Define material properties</t>
+  </si>
+  <si>
+    <t>Build structural geometry</t>
+  </si>
+  <si>
+    <t>Define supports and links</t>
+  </si>
+  <si>
+    <t>Input tendon profile</t>
+  </si>
+  <si>
+    <t>Define bridge loads</t>
+  </si>
+  <si>
+    <t>Build staged construction</t>
+  </si>
+  <si>
+    <t>Input soil spring parameters</t>
+  </si>
+  <si>
+    <t>project_name</t>
+  </si>
+  <si>
+    <t>template_name</t>
+  </si>
+  <si>
+    <t>deadline</t>
+  </si>
+  <si>
+    <t>buffer_days</t>
+  </si>
+  <si>
+    <t>CES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jembatan Medan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jembatan Jakarta </t>
+  </si>
+  <si>
+    <t>Gambar Struktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holes Location </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tendon top plan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tendon bottom plan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side view tendon top &amp; coordinates </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side view tendon bottom &amp; coordinates </t>
+  </si>
+  <si>
+    <t>Detailing</t>
+  </si>
+  <si>
+    <t>Gambar struktur utama secara keseluruhan</t>
+  </si>
+  <si>
+    <t>Plotting lubang spare FT</t>
+  </si>
+  <si>
+    <t>Skematik tendon</t>
+  </si>
+  <si>
+    <t>Gambar tampak denah tendon top</t>
+  </si>
+  <si>
+    <t>Gambar tampak denah tendon bottom</t>
+  </si>
+  <si>
+    <t>Gambar tampak samping tendon top dan koordinat Y1, Y2, dan Z</t>
+  </si>
+  <si>
+    <t>Gambar tampak samping tendon bottom dan koordinat Y1, Y2, dan Z</t>
+  </si>
+  <si>
+    <t>Gambar detailing seperti pembesian angkur, blister dan lain lain</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>FT</t>
+  </si>
+  <si>
+    <t>CES Engineer</t>
+  </si>
+  <si>
+    <t>Drafter</t>
+  </si>
+  <si>
+    <t>Jacking force</t>
+  </si>
+  <si>
+    <t>Pressure jack calculation</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>Gambar Skematik</t>
+  </si>
+  <si>
+    <t>Cek part/detailing</t>
+  </si>
+  <si>
+    <t>FT Loadings</t>
+  </si>
+  <si>
+    <t>FT Bottom</t>
+  </si>
+  <si>
+    <t>FT Drive deck &amp; cantilever</t>
+  </si>
+  <si>
+    <t>FT Main Frame</t>
+  </si>
+  <si>
+    <t>PPT Report</t>
+  </si>
+  <si>
+    <t>Internal Presentation</t>
+  </si>
+  <si>
+    <t>FT Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analisa FT Bottom </t>
+  </si>
+  <si>
+    <t>Perhitungan beban FT dari box girder</t>
+  </si>
+  <si>
+    <t>analisa struktur drive deck dan kantilever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analisa struktur man frame </t>
+  </si>
+  <si>
+    <t>Reporting dalam bentuk ppt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presentasi FT </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="yyyy-mm-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="4">
@@ -320,34 +511,35 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -357,25 +549,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ff0b769f"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FF0B769F"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office Theme">
       <a:dk1>
@@ -577,7 +829,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -595,7 +847,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -624,7 +876,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -649,7 +901,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -674,7 +926,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -699,7 +951,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -724,7 +976,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -749,7 +1001,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -774,7 +1026,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -799,7 +1051,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -824,7 +1076,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -837,9 +1089,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -856,7 +1114,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -874,7 +1132,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -899,7 +1157,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -924,7 +1182,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -949,7 +1207,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -974,7 +1232,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -999,7 +1257,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1024,7 +1282,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1049,7 +1307,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1074,7 +1332,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1099,7 +1357,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1112,9 +1370,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1128,7 +1392,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1146,7 +1410,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1175,7 +1439,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1200,7 +1464,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1225,7 +1489,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1250,7 +1514,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1275,7 +1539,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1300,7 +1564,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1325,7 +1589,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1350,7 +1614,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1375,7 +1639,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1388,66 +1652,74 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.3516" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.8516" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6719" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.0625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.1719" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1719" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.3516" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85156" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.69921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.09765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.19921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.19921875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.796875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:7" ht="16.05" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="3">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="3">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="3">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="3">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="3">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="3">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" spans="1:7" ht="16.05" customHeight="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" t="s" s="3">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="5"/>
-      <c r="D2" t="s" s="3">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s" s="3">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="6">
@@ -1457,18 +1729,18 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" spans="1:7" ht="16.05" customHeight="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" t="s" s="3">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="5"/>
-      <c r="D3" t="s" s="3">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s" s="3">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="6">
@@ -1478,18 +1750,18 @@
         <v>45662</v>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" spans="1:7" ht="16.05" customHeight="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" t="s" s="3">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="5"/>
-      <c r="D4" t="s" s="3">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s" s="3">
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="6">
@@ -1499,18 +1771,18 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" spans="1:7" ht="16.05" customHeight="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" t="s" s="3">
+      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="5"/>
-      <c r="D5" t="s" s="3">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s" s="3">
+      <c r="E5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="6">
@@ -1520,20 +1792,20 @@
         <v>45666</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
+    <row r="6" spans="1:7" ht="16.05" customHeight="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" t="s" s="3">
+      <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
-      <c r="D6" t="s" s="3">
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" t="s" s="3">
+      <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="6">
@@ -1543,20 +1815,20 @@
         <v>45669</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7" spans="1:7" ht="16.05" customHeight="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" t="s" s="3">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="7">
         <v>2</v>
       </c>
-      <c r="D7" t="s" s="3">
+      <c r="D7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s" s="3">
+      <c r="E7" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="6">
@@ -1566,20 +1838,20 @@
         <v>45670</v>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
+    <row r="8" spans="1:7" ht="16.05" customHeight="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" t="s" s="3">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="7">
         <v>3</v>
       </c>
-      <c r="D8" t="s" s="3">
+      <c r="D8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="s" s="3">
+      <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="6">
@@ -1589,20 +1861,20 @@
         <v>45673</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9" spans="1:7" ht="16.05" customHeight="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" t="s" s="3">
+      <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="7">
         <v>4</v>
       </c>
-      <c r="D9" t="s" s="3">
+      <c r="D9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s" s="3">
+      <c r="E9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="6">
@@ -1612,18 +1884,18 @@
         <v>45674</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10" spans="1:7" ht="16.05" customHeight="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" t="s" s="3">
+      <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="5"/>
-      <c r="D10" t="s" s="3">
+      <c r="D10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E10" t="s" s="3">
+      <c r="E10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="6">
@@ -1633,20 +1905,20 @@
         <v>45677</v>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" spans="1:7" ht="16.05" customHeight="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" t="s" s="3">
+      <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="7">
         <v>7</v>
       </c>
-      <c r="D11" t="s" s="3">
+      <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E11" t="s" s="3">
+      <c r="E11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="6">
@@ -1656,18 +1928,18 @@
         <v>45680</v>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
+    <row r="12" spans="1:7" ht="16.05" customHeight="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" t="s" s="3">
+      <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="5"/>
-      <c r="D12" t="s" s="3">
+      <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E12" t="s" s="3">
+      <c r="E12" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="6">
@@ -1677,18 +1949,18 @@
         <v>45683</v>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
+    <row r="13" spans="1:7" ht="16.05" customHeight="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" t="s" s="3">
+      <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="5"/>
-      <c r="D13" t="s" s="3">
+      <c r="D13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E13" t="s" s="3">
+      <c r="E13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F13" s="6">
@@ -1698,20 +1970,20 @@
         <v>45687</v>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
+    <row r="14" spans="1:7" ht="16.05" customHeight="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" t="s" s="3">
+      <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="7">
         <v>10</v>
       </c>
-      <c r="D14" t="s" s="3">
+      <c r="D14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E14" t="s" s="3">
+      <c r="E14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F14" s="6">
@@ -1721,20 +1993,20 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15" spans="1:7" ht="16.05" customHeight="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" t="s" s="3">
+      <c r="B15" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="7">
         <v>9</v>
       </c>
-      <c r="D15" t="s" s="3">
+      <c r="D15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E15" t="s" s="3">
+      <c r="E15" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F15" s="6">
@@ -1744,20 +2016,20 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
+    <row r="16" spans="1:7" ht="16.05" customHeight="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" t="s" s="3">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="7">
         <v>6</v>
       </c>
-      <c r="D16" t="s" s="3">
+      <c r="D16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E16" t="s" s="3">
+      <c r="E16" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F16" s="6">
@@ -1767,18 +2039,18 @@
         <v>45694</v>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
+    <row r="17" spans="1:7" ht="16.05" customHeight="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" t="s" s="3">
+      <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="5"/>
-      <c r="D17" t="s" s="3">
+      <c r="D17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E17" t="s" s="3">
+      <c r="E17" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F17" s="6">
@@ -1788,18 +2060,18 @@
         <v>45709</v>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
+    <row r="18" spans="1:7" ht="16.05" customHeight="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" t="s" s="3">
+      <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="5"/>
-      <c r="D18" t="s" s="3">
+      <c r="D18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E18" t="s" s="3">
+      <c r="E18" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F18" s="6">
@@ -1809,18 +2081,18 @@
         <v>45698</v>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
+    <row r="19" spans="1:7" ht="16.05" customHeight="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" t="s" s="3">
+      <c r="B19" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="5"/>
-      <c r="D19" t="s" s="3">
+      <c r="D19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E19" t="s" s="3">
+      <c r="E19" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F19" s="6">
@@ -1830,20 +2102,20 @@
         <v>45704</v>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
+    <row r="20" spans="1:7" ht="16.05" customHeight="1">
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" t="s" s="3">
+      <c r="B20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="7">
         <v>13</v>
       </c>
-      <c r="D20" t="s" s="3">
+      <c r="D20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E20" t="s" s="3">
+      <c r="E20" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F20" s="6">
@@ -1853,20 +2125,20 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
+    <row r="21" spans="1:7" ht="16.05" customHeight="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" t="s" s="3">
+      <c r="B21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="7">
         <v>15</v>
       </c>
-      <c r="D21" t="s" s="3">
+      <c r="D21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E21" t="s" s="3">
+      <c r="E21" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F21" s="6">
@@ -1876,18 +2148,18 @@
         <v>45709</v>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
+    <row r="22" spans="1:7" ht="16.05" customHeight="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" t="s" s="3">
+      <c r="B22" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="5"/>
-      <c r="D22" t="s" s="3">
+      <c r="D22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E22" t="s" s="3">
+      <c r="E22" s="3" t="s">
         <v>45</v>
       </c>
       <c r="F22" s="6">
@@ -1897,18 +2169,18 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
+    <row r="23" spans="1:7" ht="16.05" customHeight="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" t="s" s="3">
+      <c r="B23" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="5"/>
-      <c r="D23" t="s" s="3">
+      <c r="D23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E23" t="s" s="3">
+      <c r="E23" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F23" s="6">
@@ -1918,20 +2190,20 @@
         <v>45743</v>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
+    <row r="24" spans="1:7" ht="16.05" customHeight="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" t="s" s="3">
+      <c r="B24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="7">
         <v>19</v>
       </c>
-      <c r="D24" t="s" s="3">
+      <c r="D24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E24" t="s" s="3">
+      <c r="E24" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F24" s="6">
@@ -1941,18 +2213,18 @@
         <v>45719</v>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
+    <row r="25" spans="1:7" ht="16.05" customHeight="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" t="s" s="3">
+      <c r="B25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="5"/>
-      <c r="D25" t="s" s="3">
+      <c r="D25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E25" t="s" s="3">
+      <c r="E25" s="3" t="s">
         <v>50</v>
       </c>
       <c r="F25" s="6">
@@ -1962,20 +2234,20 @@
         <v>45753</v>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
+    <row r="26" spans="1:7" ht="16.05" customHeight="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" t="s" s="3">
+      <c r="B26" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="7">
         <v>17</v>
       </c>
-      <c r="D26" t="s" s="3">
+      <c r="D26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E26" t="s" s="3">
+      <c r="E26" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F26" s="6">
@@ -1985,18 +2257,18 @@
         <v>45725</v>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1">
+    <row r="27" spans="1:7" ht="16.05" customHeight="1">
       <c r="A27" s="7">
         <v>31</v>
       </c>
-      <c r="B27" t="s" s="3">
+      <c r="B27" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="5"/>
-      <c r="D27" t="s" s="3">
+      <c r="D27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E27" t="s" s="3">
+      <c r="E27" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F27" s="6">
@@ -2006,18 +2278,18 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
+    <row r="28" spans="1:7" ht="16.05" customHeight="1">
       <c r="A28" s="7">
         <v>32</v>
       </c>
-      <c r="B28" t="s" s="3">
+      <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="5"/>
-      <c r="D28" t="s" s="3">
+      <c r="D28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E28" t="s" s="3">
+      <c r="E28" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F28" s="6">
@@ -2027,18 +2299,18 @@
         <v>45751</v>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
+    <row r="29" spans="1:7" ht="16.05" customHeight="1">
       <c r="A29" s="7">
         <v>33</v>
       </c>
-      <c r="B29" t="s" s="3">
+      <c r="B29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C29" s="5"/>
-      <c r="D29" t="s" s="3">
+      <c r="D29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E29" t="s" s="3">
+      <c r="E29" s="3" t="s">
         <v>57</v>
       </c>
       <c r="F29" s="6">
@@ -2048,18 +2320,18 @@
         <v>45754</v>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
+    <row r="30" spans="1:7" ht="16.05" customHeight="1">
       <c r="A30" s="7">
         <v>34</v>
       </c>
-      <c r="B30" t="s" s="3">
+      <c r="B30" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="5"/>
-      <c r="D30" t="s" s="3">
+      <c r="D30" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E30" t="s" s="3">
+      <c r="E30" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F30" s="6">
@@ -2069,20 +2341,20 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
+    <row r="31" spans="1:7" ht="16.05" customHeight="1">
       <c r="A31" s="7">
         <v>35</v>
       </c>
-      <c r="B31" t="s" s="3">
+      <c r="B31" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="7">
         <v>31</v>
       </c>
-      <c r="D31" t="s" s="3">
+      <c r="D31" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E31" t="s" s="3">
+      <c r="E31" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F31" s="6">
@@ -2092,20 +2364,20 @@
         <v>45761</v>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
+    <row r="32" spans="1:7" ht="16.05" customHeight="1">
       <c r="A32" s="7">
         <v>36</v>
       </c>
-      <c r="B32" t="s" s="3">
+      <c r="B32" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C32" s="7">
         <v>33</v>
       </c>
-      <c r="D32" t="s" s="3">
+      <c r="D32" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E32" t="s" s="3">
+      <c r="E32" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F32" s="6">
@@ -2115,20 +2387,20 @@
         <v>45766</v>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1">
+    <row r="33" spans="1:7" ht="16.05" customHeight="1">
       <c r="A33" s="7">
         <v>37</v>
       </c>
-      <c r="B33" t="s" s="3">
+      <c r="B33" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="7">
         <v>34</v>
       </c>
-      <c r="D33" t="s" s="3">
+      <c r="D33" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E33" t="s" s="3">
+      <c r="E33" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F33" s="6">
@@ -2138,18 +2410,18 @@
         <v>45768</v>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1">
+    <row r="34" spans="1:7" ht="16.05" customHeight="1">
       <c r="A34" s="7">
         <v>38</v>
       </c>
-      <c r="B34" t="s" s="3">
+      <c r="B34" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="5"/>
-      <c r="D34" t="s" s="3">
+      <c r="D34" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E34" t="s" s="3">
+      <c r="E34" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F34" s="6">
@@ -2159,18 +2431,18 @@
         <v>45773</v>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
+    <row r="35" spans="1:7" ht="16.05" customHeight="1">
       <c r="A35" s="7">
         <v>39</v>
       </c>
-      <c r="B35" t="s" s="3">
+      <c r="B35" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="5"/>
-      <c r="D35" t="s" s="3">
+      <c r="D35" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E35" t="s" s="3">
+      <c r="E35" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F35" s="6">
@@ -2180,18 +2452,18 @@
         <v>45775</v>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
+    <row r="36" spans="1:7" ht="16.05" customHeight="1">
       <c r="A36" s="7">
         <v>40</v>
       </c>
-      <c r="B36" t="s" s="3">
+      <c r="B36" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C36" s="5"/>
-      <c r="D36" t="s" s="3">
+      <c r="D36" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E36" t="s" s="3">
+      <c r="E36" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F36" s="6">
@@ -2201,18 +2473,18 @@
         <v>45780</v>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1">
+    <row r="37" spans="1:7" ht="16.05" customHeight="1">
       <c r="A37" s="7">
         <v>41</v>
       </c>
-      <c r="B37" t="s" s="3">
+      <c r="B37" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="5"/>
-      <c r="D37" t="s" s="3">
+      <c r="D37" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E37" t="s" s="3">
+      <c r="E37" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F37" s="6">
@@ -2222,18 +2494,18 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
+    <row r="38" spans="1:7" ht="16.05" customHeight="1">
       <c r="A38" s="7">
         <v>42</v>
       </c>
-      <c r="B38" t="s" s="3">
+      <c r="B38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="5"/>
-      <c r="D38" t="s" s="3">
+      <c r="D38" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E38" t="s" s="3">
+      <c r="E38" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F38" s="6">
@@ -2243,18 +2515,18 @@
         <v>45788</v>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
+    <row r="39" spans="1:7" ht="16.05" customHeight="1">
       <c r="A39" s="7">
         <v>43</v>
       </c>
-      <c r="B39" t="s" s="3">
+      <c r="B39" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="5"/>
-      <c r="D39" t="s" s="3">
+      <c r="D39" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E39" t="s" s="3">
+      <c r="E39" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F39" s="6">
@@ -2264,18 +2536,18 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
+    <row r="40" spans="1:7" ht="16.05" customHeight="1">
       <c r="A40" s="7">
         <v>44</v>
       </c>
-      <c r="B40" t="s" s="3">
+      <c r="B40" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C40" s="5"/>
-      <c r="D40" t="s" s="3">
+      <c r="D40" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E40" t="s" s="3">
+      <c r="E40" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F40" s="6">
@@ -2285,18 +2557,18 @@
         <v>45795</v>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1">
+    <row r="41" spans="1:7" ht="16.05" customHeight="1">
       <c r="A41" s="7">
         <v>45</v>
       </c>
-      <c r="B41" t="s" s="3">
+      <c r="B41" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="5"/>
-      <c r="D41" t="s" s="3">
+      <c r="D41" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E41" t="s" s="3">
+      <c r="E41" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F41" s="6">
@@ -2308,9 +2580,718 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31EC9A9-AD0A-41E7-A100-17EDC0B19FA0}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="24.19921875" customWidth="1"/>
+    <col min="2" max="2" width="15.3984375" customWidth="1"/>
+    <col min="3" max="3" width="16.69921875" customWidth="1"/>
+    <col min="4" max="4" width="18.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="27.6">
+      <c r="A1" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="12">
+        <v>46234</v>
+      </c>
+      <c r="D2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="12">
+        <v>46234</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="12">
+        <v>46234</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="12">
+        <v>46234</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="12">
+        <v>46234</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="12">
+        <v>46234</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E09EFC7-D621-4DB9-B3DB-46D042D75FB1}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="2" max="3" width="16.296875" customWidth="1"/>
+    <col min="4" max="4" width="22.69921875" customWidth="1"/>
+    <col min="5" max="5" width="15.296875" customWidth="1"/>
+    <col min="6" max="6" width="22.09765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="9">
+        <v>2</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="9">
+        <v>1</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="27.6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11">
+        <v>2</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="9">
+        <v>3</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="27.6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="9">
+        <v>2</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11">
+        <v>3</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="9">
+        <v>2</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11">
+        <v>5</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="9">
+        <v>2</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="41.4">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11">
+        <v>6</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="9">
+        <v>4</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="27.6">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11">
+        <v>7</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11">
+        <v>4</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="9">
+        <v>14</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="E12">
+        <f>SUM(E2:E10)</f>
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2752EED-A9B6-47DA-B5DE-1590152C08D6}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="2" max="2" width="17.796875" customWidth="1"/>
+    <col min="3" max="3" width="19.69921875" customWidth="1"/>
+    <col min="4" max="4" width="26.8984375" customWidth="1"/>
+    <col min="5" max="5" width="15.69921875" customWidth="1"/>
+    <col min="6" max="6" width="21.296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="27.6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="9">
+        <v>2</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="9">
+        <v>1</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11">
+        <v>2</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="9">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="27.6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="9">
+        <v>3</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="27.6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11">
+        <v>4</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="9">
+        <v>2</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="41.4">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11">
+        <v>5</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="9">
+        <v>2</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="41.4">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11">
+        <v>6</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="41.4">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11">
+        <v>7</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="9">
+        <v>4</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFF7D4E-F706-4B78-8D83-192647177D23}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.8984375" customWidth="1"/>
+    <col min="3" max="3" width="21.3984375" customWidth="1"/>
+    <col min="4" max="4" width="35.19921875" customWidth="1"/>
+    <col min="5" max="5" width="20.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="27.6">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="9">
+        <v>1</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="27.6">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="9">
+        <v>2</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="27.6">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11">
+        <v>2</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="9">
+        <v>3</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="27.6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="9">
+        <v>3</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="27.6">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11">
+        <v>4</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="9">
+        <v>3</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="27.6">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11">
+        <v>5</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="9">
+        <v>3</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="27.6">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11">
+        <v>6</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/project_tasks.xlsx
+++ b/data/project_tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\WW FILES\Indie Project\gantt-plotter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E275D26C-4E60-45D0-95EE-DAF22B6E1724}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD14A596-B028-4A21-B9EE-42652B71123D}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="36" windowWidth="15960" windowHeight="18084" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="36" windowWidth="15960" windowHeight="18084" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -320,9 +320,6 @@
     <t>template_name</t>
   </si>
   <si>
-    <t>deadline</t>
-  </si>
-  <si>
     <t>buffer_days</t>
   </si>
   <si>
@@ -444,6 +441,9 @@
   </si>
   <si>
     <t xml:space="preserve">Presentasi FT </t>
+  </si>
+  <si>
+    <t>startline</t>
   </si>
 </sst>
 </file>
@@ -2598,7 +2598,7 @@
     <col min="4" max="4" width="18.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27.6">
+    <row r="1" spans="1:4">
       <c r="A1" s="8" t="s">
         <v>96</v>
       </c>
@@ -2606,18 +2606,18 @@
         <v>97</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C2" s="12">
         <v>46234</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="12">
         <v>46234</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="12">
         <v>46234</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="12">
         <v>46234</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C6" s="12">
         <v>46234</v>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="12">
         <v>46234</v>
@@ -2731,7 +2731,7 @@
         <v>87</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2749,7 +2749,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2769,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27.6">
@@ -2789,7 +2789,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.6">
@@ -2809,7 +2809,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2829,7 +2829,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2849,7 +2849,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="41.4">
@@ -2869,7 +2869,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27.6">
@@ -2889,7 +2889,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2900,16 +2900,16 @@
         <v>4</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>123</v>
       </c>
       <c r="E10" s="9">
         <v>14</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2952,7 +2952,7 @@
         <v>87</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="27.6">
@@ -2961,16 +2961,16 @@
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" s="9">
         <v>2</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2981,16 +2981,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3001,16 +3001,16 @@
         <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" s="9">
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.6">
@@ -3021,16 +3021,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5" s="9">
         <v>3</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.6">
@@ -3041,16 +3041,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E6" s="9">
         <v>2</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="41.4">
@@ -3061,16 +3061,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E7" s="9">
         <v>2</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="41.4">
@@ -3081,16 +3081,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E8" s="9">
         <v>2</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="41.4">
@@ -3101,16 +3101,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E9" s="9">
         <v>4</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3150,7 +3150,7 @@
         <v>87</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="27.6">
@@ -3159,16 +3159,16 @@
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" s="9">
         <v>1</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27.6">
@@ -3179,16 +3179,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E3" s="9">
         <v>2</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27.6">
@@ -3199,16 +3199,16 @@
         <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="9">
         <v>3</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.6">
@@ -3219,16 +3219,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E5" s="9">
         <v>3</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.6">
@@ -3239,16 +3239,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E6" s="9">
         <v>3</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27.6">
@@ -3259,16 +3259,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E7" s="9">
         <v>3</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27.6">
@@ -3279,16 +3279,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E8" s="9">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/data/project_tasks.xlsx
+++ b/data/project_tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\WW FILES\Indie Project\gantt-plotter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD14A596-B028-4A21-B9EE-42652B71123D}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1183BEC7-1C1E-42C2-AB41-8D656506F61F}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="36" windowWidth="15960" windowHeight="18084" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="144">
   <si>
     <t>task_id</t>
   </si>
@@ -263,57 +263,24 @@
     <t>Create loyalty program</t>
   </si>
   <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>Structure Geometry</t>
-  </si>
-  <si>
-    <t>Boundary Condition</t>
-  </si>
-  <si>
-    <t>Tendon</t>
-  </si>
-  <si>
     <t>Bridge Loading</t>
   </si>
   <si>
-    <t>Construction Sequence &amp; Method</t>
-  </si>
-  <si>
     <t>SSI Parameter</t>
   </si>
   <si>
     <t>duration_days</t>
   </si>
   <si>
-    <t>Review section input</t>
-  </si>
-  <si>
-    <t>Define material properties</t>
-  </si>
-  <si>
-    <t>Build structural geometry</t>
-  </si>
-  <si>
     <t>Define supports and links</t>
   </si>
   <si>
     <t>Input tendon profile</t>
   </si>
   <si>
-    <t>Define bridge loads</t>
-  </si>
-  <si>
     <t>Build staged construction</t>
   </si>
   <si>
-    <t>Input soil spring parameters</t>
-  </si>
-  <si>
     <t>project_name</t>
   </si>
   <si>
@@ -419,9 +386,6 @@
     <t>PPT Report</t>
   </si>
   <si>
-    <t>Internal Presentation</t>
-  </si>
-  <si>
     <t>FT Engineer</t>
   </si>
   <si>
@@ -440,10 +404,58 @@
     <t>Reporting dalam bentuk ppt</t>
   </si>
   <si>
-    <t xml:space="preserve">Presentasi FT </t>
-  </si>
-  <si>
     <t>startline</t>
+  </si>
+  <si>
+    <t>Supporting Engineer</t>
+  </si>
+  <si>
+    <t>Section &amp; Material Input</t>
+  </si>
+  <si>
+    <t>Defining section and material properties</t>
+  </si>
+  <si>
+    <t>Stucture Geometry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundary Condition </t>
+  </si>
+  <si>
+    <t>Tendon Input</t>
+  </si>
+  <si>
+    <t>Construction Sequence Model</t>
+  </si>
+  <si>
+    <t>Seismic Construction Analysis</t>
+  </si>
+  <si>
+    <t>Construction Stage Analysis</t>
+  </si>
+  <si>
+    <t>SLS Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analysis for seismic construction </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sequential stress check </t>
+  </si>
+  <si>
+    <t>Analysis for service coondition</t>
+  </si>
+  <si>
+    <t>Report Preparation</t>
+  </si>
+  <si>
+    <t>Report / PPT</t>
+  </si>
+  <si>
+    <t>Define bridge loads, construction and service loading</t>
+  </si>
+  <si>
+    <t>Construct structural frame</t>
   </si>
 </sst>
 </file>
@@ -2600,27 +2612,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="8" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="11" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C2" s="12">
-        <v>46234</v>
+        <v>46204</v>
       </c>
       <c r="D2" s="9">
         <v>0</v>
@@ -2628,13 +2640,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="11" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C3" s="12">
-        <v>46234</v>
+        <v>46204</v>
       </c>
       <c r="D3" s="9">
         <v>0</v>
@@ -2642,13 +2654,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="11" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C4" s="12">
-        <v>46234</v>
+        <v>46204</v>
       </c>
       <c r="D4" s="9">
         <v>0</v>
@@ -2656,13 +2668,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C5" s="12">
-        <v>46234</v>
+        <v>46204</v>
       </c>
       <c r="D5" s="9">
         <v>0</v>
@@ -2670,13 +2682,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C6" s="12">
-        <v>46234</v>
+        <v>46204</v>
       </c>
       <c r="D6" s="9">
         <v>0</v>
@@ -2684,13 +2696,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C7" s="12">
-        <v>46234</v>
+        <v>46204</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -2704,12 +2716,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E09EFC7-D621-4DB9-B3DB-46D042D75FB1}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13.59765625" customWidth="1"/>
-    <col min="2" max="3" width="16.296875" customWidth="1"/>
-    <col min="4" max="4" width="22.69921875" customWidth="1"/>
+    <col min="2" max="2" width="16.296875" customWidth="1"/>
+    <col min="3" max="3" width="38.5" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="15.296875" customWidth="1"/>
     <col min="6" max="6" width="22.09765625" customWidth="1"/>
   </cols>
@@ -2728,28 +2741,28 @@
         <v>4</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="27.6">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="E2" s="9">
         <v>2</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2760,19 +2773,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="E3" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="27.6">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2780,36 +2793,36 @@
         <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E4" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="27.6">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="11">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="9">
         <v>3</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="9">
-        <v>2</v>
-      </c>
       <c r="F5" s="11" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2820,19 +2833,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="E6" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="27.6">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -2840,19 +2853,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="E7" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="41.4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -2860,19 +2873,19 @@
         <v>6</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E8" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="27.6">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -2880,16 +2893,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="E9" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2897,25 +2910,85 @@
         <v>9</v>
       </c>
       <c r="B10" s="11">
+        <v>8</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10" s="9">
+        <v>5</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="9">
+        <v>5</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11">
+        <v>10</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="9">
+        <v>8</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11">
         <v>4</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="9">
-        <v>14</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="E12">
-        <f>SUM(E2:E10)</f>
-        <v>32</v>
+      <c r="C13" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="9">
+        <v>7</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="F16">
+        <f>SUMIF(F2:F13,"CES Engineer",E2:E13)</f>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2925,7 +2998,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2752EED-A9B6-47DA-B5DE-1590152C08D6}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="17.796875" customWidth="1"/>
@@ -2949,10 +3022,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="27.6">
@@ -2961,16 +3034,16 @@
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E2" s="9">
         <v>2</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2981,16 +3054,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E3" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3001,16 +3074,16 @@
         <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E4" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.6">
@@ -3021,16 +3094,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E5" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.6">
@@ -3041,16 +3114,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E6" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="41.4">
@@ -3061,16 +3134,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E7" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="41.4">
@@ -3081,16 +3154,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E8" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="41.4">
@@ -3101,20 +3174,26 @@
         <v>7</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="E9" s="9">
         <v>4</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" s="11"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="F11">
+        <f>SUM(E2:E9)</f>
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3123,7 +3202,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFF7D4E-F706-4B78-8D83-192647177D23}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="7.09765625" bestFit="1" customWidth="1"/>
@@ -3147,10 +3226,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="27.6">
@@ -3159,16 +3238,16 @@
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E2" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27.6">
@@ -3179,16 +3258,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E3" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27.6">
@@ -3199,16 +3278,16 @@
         <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E4" s="9">
         <v>3</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.6">
@@ -3219,16 +3298,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E5" s="9">
         <v>3</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.6">
@@ -3239,16 +3318,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E6" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27.6">
@@ -3259,36 +3338,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E7" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="27.6">
-      <c r="A8" s="9">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11">
-        <v>6</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" s="9">
-        <v>1</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>132</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="F9">
+        <f>SUM(E2:E7)</f>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/project_tasks.xlsx
+++ b/data/project_tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\WW FILES\Indie Project\gantt-plotter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1183BEC7-1C1E-42C2-AB41-8D656506F61F}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F689B3-3E71-464D-A568-E95D79D35DAE}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="36" windowWidth="15960" windowHeight="18084" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="36" windowWidth="15960" windowHeight="18084" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="145">
   <si>
     <t>task_id</t>
   </si>
@@ -456,6 +456,9 @@
   </si>
   <si>
     <t>Construct structural frame</t>
+  </si>
+  <si>
+    <t>deadline</t>
   </si>
 </sst>
 </file>
@@ -2601,16 +2604,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31EC9A9-AD0A-41E7-A100-17EDC0B19FA0}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="24.19921875" customWidth="1"/>
-    <col min="2" max="2" width="15.3984375" customWidth="1"/>
-    <col min="3" max="3" width="16.69921875" customWidth="1"/>
-    <col min="4" max="4" width="18.796875" customWidth="1"/>
+    <col min="2" max="3" width="15.3984375" customWidth="1"/>
+    <col min="4" max="4" width="16.69921875" customWidth="1"/>
+    <col min="5" max="5" width="18.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="8" t="s">
         <v>85</v>
       </c>
@@ -2618,55 +2621,61 @@
         <v>86</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="11" t="s">
         <v>89</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11"/>
+      <c r="D2" s="12">
         <v>46204</v>
       </c>
-      <c r="D2" s="9">
+      <c r="E2" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="11" t="s">
         <v>89</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11"/>
+      <c r="D3" s="12">
         <v>46204</v>
       </c>
-      <c r="D3" s="9">
+      <c r="E3" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="11" t="s">
         <v>89</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11"/>
+      <c r="D4" s="12">
         <v>46204</v>
       </c>
-      <c r="D4" s="9">
+      <c r="E4" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -2674,37 +2683,40 @@
         <v>88</v>
       </c>
       <c r="C5" s="12">
-        <v>46204</v>
-      </c>
-      <c r="D5" s="9">
+        <v>46235</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>90</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="12">
-        <v>46204</v>
-      </c>
-      <c r="D6" s="9">
+      <c r="C6" s="12"/>
+      <c r="D6" s="12">
+        <v>46199</v>
+      </c>
+      <c r="E6" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>90</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="12">
-        <v>46204</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="C7" s="12"/>
+      <c r="D7" s="12">
+        <v>46199</v>
+      </c>
+      <c r="E7" s="9">
         <v>0</v>
       </c>
     </row>
